--- a/data.xlsx
+++ b/data.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\yupi kong mahal\zzz Career Hub\1 Vekt Data Lab\fund-stat-analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10180" windowHeight="5770"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Copy of Clean Data" sheetId="1" r:id="rId5"/>
+    <sheet name="Copy of Clean Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="80">
   <si>
     <t>No.</t>
   </si>
@@ -220,9 +228,6 @@
     <t>Sun Life Prosperity Achiever Fund 2028</t>
   </si>
   <si>
-    <t>69,79,820.69</t>
-  </si>
-  <si>
     <t>6 years</t>
   </si>
   <si>
@@ -242,9 +247,6 @@
   </si>
   <si>
     <t>Sun Life Prosperity Wolrd Voyage Fund</t>
-  </si>
-  <si>
-    <t>85,94,442.21</t>
   </si>
   <si>
     <t>10 years</t>
@@ -262,68 +264,86 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -337,6 +357,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -351,141 +372,110 @@
       <bottom style="thin">
         <color rgb="FFAAAAAA"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+  <cellXfs count="32">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -502,20 +492,48 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Copy of Clean Data-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Copy of Clean Data-style" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -523,35 +541,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:T27" displayName="Table3" name="Table3" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:T27">
   <tableColumns count="20">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Company Name / Investment Manager" id="2"/>
-    <tableColumn name="Fund Name" id="3"/>
-    <tableColumn name="Fund Type" id="4"/>
-    <tableColumn name="Investment Style" id="5"/>
-    <tableColumn name="Fund Return (YTD)" id="6"/>
-    <tableColumn name="Fund Return (2025)" id="7"/>
-    <tableColumn name="Benchmark Return" id="8"/>
-    <tableColumn name="Effective Period Change" id="9"/>
-    <tableColumn name="Actual (1-YR)" id="10"/>
-    <tableColumn name="Predicted" id="11"/>
-    <tableColumn name="Fund Size 2025" id="12"/>
-    <tableColumn name="Fund Size 2026" id="13"/>
-    <tableColumn name="Expense Ratio (%)" id="14"/>
-    <tableColumn name="Front / Rear Load (%)" id="15"/>
-    <tableColumn name="Fund Flow" id="16"/>
-    <tableColumn name="Flow Volatility (annualized)" id="17"/>
-    <tableColumn name="Boook to Market" id="18"/>
-    <tableColumn name="Momentum (Y2025 return)" id="19"/>
-    <tableColumn name="Fund Age (Years)" id="20"/>
+    <tableColumn id="1" name="No."/>
+    <tableColumn id="2" name="Company Name / Investment Manager"/>
+    <tableColumn id="3" name="Fund Name"/>
+    <tableColumn id="4" name="Fund Type"/>
+    <tableColumn id="5" name="Investment Style"/>
+    <tableColumn id="6" name="Fund Return (YTD)"/>
+    <tableColumn id="7" name="Fund Return (2025)"/>
+    <tableColumn id="8" name="Benchmark Return"/>
+    <tableColumn id="9" name="Effective Period Change"/>
+    <tableColumn id="10" name="Actual (1-YR)"/>
+    <tableColumn id="11" name="Predicted"/>
+    <tableColumn id="12" name="Fund Size 2025"/>
+    <tableColumn id="13" name="Fund Size 2026"/>
+    <tableColumn id="14" name="Expense Ratio (%)"/>
+    <tableColumn id="15" name="Front / Rear Load (%)"/>
+    <tableColumn id="16" name="Fund Flow"/>
+    <tableColumn id="17" name="Flow Volatility (annualized)"/>
+    <tableColumn id="18" name="Boook to Market"/>
+    <tableColumn id="19" name="Momentum (Y2025 return)"/>
+    <tableColumn id="20" name="Fund Age (Years)"/>
   </tableColumns>
-  <tableStyleInfo name="Copy of Clean Data-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Copy of Clean Data-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -741,35 +759,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:T27"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.13"/>
-    <col customWidth="1" min="2" max="2" width="41.63"/>
-    <col customWidth="1" min="3" max="3" width="48.63"/>
-    <col customWidth="1" min="4" max="5" width="22.88"/>
-    <col customWidth="1" min="6" max="6" width="21.63"/>
-    <col customWidth="1" min="7" max="7" width="21.13"/>
-    <col customWidth="1" min="8" max="8" width="21.38"/>
-    <col customWidth="1" min="9" max="9" width="21.13"/>
-    <col customWidth="1" min="11" max="12" width="25.63"/>
-    <col customWidth="1" min="13" max="13" width="23.75"/>
-    <col customWidth="1" min="14" max="14" width="21.0"/>
-    <col customWidth="1" min="15" max="16" width="35.25"/>
-    <col customWidth="1" min="17" max="17" width="22.0"/>
-    <col customWidth="1" min="18" max="18" width="28.13"/>
-    <col customWidth="1" min="19" max="19" width="25.63"/>
-    <col customWidth="1" min="20" max="20" width="29.25"/>
+    <col min="1" max="1" width="8.08984375" customWidth="1"/>
+    <col min="2" max="2" width="41.6328125" customWidth="1"/>
+    <col min="3" max="3" width="48.6328125" customWidth="1"/>
+    <col min="4" max="5" width="22.90625" customWidth="1"/>
+    <col min="6" max="6" width="21.6328125" customWidth="1"/>
+    <col min="7" max="7" width="21.08984375" customWidth="1"/>
+    <col min="8" max="8" width="21.36328125" customWidth="1"/>
+    <col min="9" max="9" width="21.08984375" customWidth="1"/>
+    <col min="11" max="12" width="25.6328125" customWidth="1"/>
+    <col min="13" max="13" width="23.7265625" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="16" width="35.26953125" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="28.08984375" customWidth="1"/>
+    <col min="19" max="19" width="25.6328125" customWidth="1"/>
+    <col min="20" max="20" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1">
+    <row r="1" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -831,9 +852,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>20</v>
@@ -848,28 +869,28 @@
         <v>23</v>
       </c>
       <c r="F2" s="6">
-        <v>0.0098</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="G2" s="6">
-        <v>0.0032</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="H2" s="7">
-        <v>0.0115</v>
+        <v>1.15E-2</v>
       </c>
       <c r="I2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="5">
-        <v>0.0091</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="K2" s="8">
-        <v>0.0081</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="L2" s="8">
-        <v>6.3811602312E9</v>
+        <v>6381160231.1999998</v>
       </c>
       <c r="M2" s="8">
-        <v>6.40178944521E9</v>
+        <v>6401789445.21</v>
       </c>
       <c r="N2" s="7">
         <v>0.01</v>
@@ -878,24 +899,24 @@
         <v>24</v>
       </c>
       <c r="P2" s="5">
-        <v>2.062921401E7</v>
+        <v>20629214.010000002</v>
       </c>
       <c r="Q2" s="7">
-        <v>0.0288</v>
+        <v>2.8799999999999999E-2</v>
       </c>
       <c r="R2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="7">
-        <v>0.0295</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>26</v>
@@ -910,31 +931,31 @@
         <v>23</v>
       </c>
       <c r="F3" s="6">
-        <v>0.0091</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="G3" s="6">
-        <v>-0.0328</v>
+        <v>-3.2800000000000003E-2</v>
       </c>
       <c r="H3" s="7">
-        <v>-0.0049</v>
+        <v>-4.8999999999999998E-3</v>
       </c>
       <c r="I3" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>0.0106</v>
+        <v>1.06E-2</v>
       </c>
       <c r="K3" s="8">
-        <v>0.0076</v>
+        <v>7.6E-3</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>28</v>
       </c>
       <c r="M3" s="8">
-        <v>2.063417548E9</v>
+        <v>2063417548</v>
       </c>
       <c r="N3" s="7">
-        <v>0.0175</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>29</v>
@@ -944,18 +965,18 @@
         <v>0.1376</v>
       </c>
       <c r="R3" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="7">
-        <v>-0.0192</v>
+        <v>-1.9199999999999998E-2</v>
       </c>
       <c r="T3" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>26</v>
@@ -970,54 +991,54 @@
         <v>32</v>
       </c>
       <c r="F4" s="6">
-        <v>0.0201</v>
+        <v>2.01E-2</v>
       </c>
       <c r="G4" s="6">
-        <v>0.0078</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="H4" s="7">
-        <v>-0.0729</v>
+        <v>-7.2900000000000006E-2</v>
       </c>
       <c r="I4" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>-0.0185</v>
+        <v>-1.8499999999999999E-2</v>
       </c>
       <c r="K4" s="10">
-        <v>-0.0215</v>
+        <v>-2.1499999999999998E-2</v>
       </c>
       <c r="L4" s="10">
-        <v>1320090.0</v>
+        <v>1320090</v>
       </c>
       <c r="M4" s="8">
-        <v>1.354317076E9</v>
+        <v>1354317076</v>
       </c>
       <c r="N4" s="7">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="P4" s="5">
-        <v>1.352996986E9</v>
+        <v>1352996986</v>
       </c>
       <c r="Q4" s="7">
-        <v>0.1405</v>
+        <v>0.14050000000000001</v>
       </c>
       <c r="R4" s="5">
-        <v>0.9998</v>
+        <v>0.99980000000000002</v>
       </c>
       <c r="S4" s="7">
-        <v>0.092</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="T4" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>34</v>
@@ -1032,52 +1053,52 @@
         <v>23</v>
       </c>
       <c r="F5" s="6">
-        <v>0.0096</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="G5" s="6">
-        <v>0.0321</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>0.0304</v>
+        <v>3.04E-2</v>
       </c>
       <c r="K5" s="11">
-        <v>0.0284</v>
+        <v>2.8400000000000002E-2</v>
       </c>
       <c r="L5" s="11">
-        <v>6.43077E8</v>
+        <v>643077000</v>
       </c>
       <c r="M5" s="11">
-        <v>2.744518092E9</v>
+        <v>2744518092</v>
       </c>
       <c r="N5" s="7">
-        <v>0.0188</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>36</v>
       </c>
       <c r="P5" s="5">
-        <v>2.101441092E9</v>
+        <v>2101441092</v>
       </c>
       <c r="Q5" s="7">
-        <v>0.0512</v>
+        <v>5.1200000000000002E-2</v>
       </c>
       <c r="R5" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="7">
-        <v>0.0663</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="T5" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>26</v>
@@ -1092,52 +1113,52 @@
         <v>23</v>
       </c>
       <c r="F6" s="6">
-        <v>0.0128</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="G6" s="6">
-        <v>0.2554</v>
+        <v>0.25540000000000002</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>0.0304</v>
+        <v>3.04E-2</v>
       </c>
       <c r="K6" s="11">
-        <v>0.0274</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="L6" s="11">
-        <v>4.1E9</v>
+        <v>4100000000</v>
       </c>
       <c r="M6" s="11">
-        <v>4.291884503E9</v>
+        <v>4291884503</v>
       </c>
       <c r="N6" s="7">
-        <v>0.0225</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>36</v>
       </c>
       <c r="P6" s="5">
-        <v>1.91884503E8</v>
+        <v>191884503</v>
       </c>
       <c r="Q6" s="7">
         <v>0.1321</v>
       </c>
       <c r="R6" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="7">
-        <v>0.0897</v>
+        <v>8.9700000000000002E-2</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>26</v>
@@ -1152,54 +1173,54 @@
         <v>23</v>
       </c>
       <c r="F7" s="6">
-        <v>0.0022</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="G7" s="6">
-        <v>0.0421</v>
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="H7" s="7">
-        <v>0.041</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="I7" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="5">
-        <v>0.0415</v>
+        <v>4.1500000000000002E-2</v>
       </c>
       <c r="K7" s="11">
-        <v>0.0405</v>
+        <v>4.0500000000000001E-2</v>
       </c>
       <c r="L7" s="11">
-        <v>2567059.0</v>
+        <v>2567059</v>
       </c>
       <c r="M7" s="11">
-        <v>1.567432195E9</v>
+        <v>1567432195</v>
       </c>
       <c r="N7" s="7">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>24</v>
       </c>
       <c r="P7" s="5">
-        <v>1.564865136E9</v>
+        <v>1564865136</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.1398</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="R7" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="7">
-        <v>0.0415</v>
+        <v>4.1500000000000002E-2</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>26</v>
@@ -1214,28 +1235,28 @@
         <v>32</v>
       </c>
       <c r="F8" s="6">
-        <v>0.0178</v>
+        <v>1.78E-2</v>
       </c>
       <c r="G8" s="6">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="H8" s="7">
-        <v>-0.0729</v>
+        <v>-7.2900000000000006E-2</v>
       </c>
       <c r="I8" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
-        <v>-0.0192</v>
+        <v>-1.9199999999999998E-2</v>
       </c>
       <c r="K8" s="11">
-        <v>-0.0222</v>
+        <v>-2.2200000000000001E-2</v>
       </c>
       <c r="L8" s="11">
-        <v>8.5317E7</v>
+        <v>85317000</v>
       </c>
       <c r="M8" s="11">
-        <v>1.29877431E9</v>
+        <v>1298774310</v>
       </c>
       <c r="N8" s="7">
         <v>0.01</v>
@@ -1244,22 +1265,22 @@
         <v>24</v>
       </c>
       <c r="P8" s="5">
-        <v>1.21345731E9</v>
+        <v>1213457310</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.1398</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="R8" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="7">
-        <v>0.0915</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="4" t="s">
         <v>44</v>
@@ -1274,48 +1295,48 @@
         <v>23</v>
       </c>
       <c r="F9" s="6">
-        <v>0.0096</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="G9" s="6">
-        <v>0.0063</v>
+        <v>6.3E-3</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="5">
-        <v>0.0214</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="K9" s="5">
-        <v>0.0194</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="11">
-        <v>1.136472214E9</v>
+        <v>1136472214</v>
       </c>
       <c r="N9" s="7">
-        <v>0.0175</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="P9" s="5">
-        <v>1.136472214E9</v>
+        <v>1136472214</v>
       </c>
       <c r="Q9" s="7">
-        <v>0.0645</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="R9" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="7">
-        <v>0.0646</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="4" t="s">
         <v>47</v>
@@ -1330,26 +1351,26 @@
         <v>23</v>
       </c>
       <c r="F10" s="6">
-        <v>0.0182</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="G10" s="6">
-        <v>0.1849</v>
+        <v>0.18490000000000001</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5">
-        <v>0.0352</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="K10" s="11">
-        <v>0.0322</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="L10" s="11">
-        <v>2747021.0</v>
+        <v>2747021</v>
       </c>
       <c r="M10" s="11">
-        <v>2.9875426E9</v>
+        <v>2987542600</v>
       </c>
       <c r="N10" s="7">
         <v>0.02</v>
@@ -1358,24 +1379,24 @@
         <v>24</v>
       </c>
       <c r="P10" s="5">
-        <v>2.984795579E9</v>
+        <v>2984795579</v>
       </c>
       <c r="Q10" s="7">
-        <v>0.0712</v>
+        <v>7.1199999999999999E-2</v>
       </c>
       <c r="R10" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="5">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>50</v>
@@ -1390,54 +1411,54 @@
         <v>23</v>
       </c>
       <c r="F11" s="6">
-        <v>0.0121</v>
+        <v>1.21E-2</v>
       </c>
       <c r="G11" s="6">
-        <v>0.0072</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="H11" s="7">
-        <v>0.0315</v>
+        <v>3.15E-2</v>
       </c>
       <c r="I11" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="5">
-        <v>0.0338</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="K11" s="11">
-        <v>0.0318</v>
+        <v>3.1800000000000002E-2</v>
       </c>
       <c r="L11" s="11">
-        <v>3.94069E8</v>
+        <v>394069000</v>
       </c>
       <c r="M11" s="11">
-        <v>3.42066191E9</v>
+        <v>3420661910</v>
       </c>
       <c r="N11" s="7">
-        <v>0.0185</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>36</v>
       </c>
       <c r="P11" s="5">
-        <v>3.02659291E9</v>
+        <v>3026592910</v>
       </c>
       <c r="Q11" s="7">
-        <v>0.0585</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="R11" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="5">
-        <v>0.0512</v>
+        <v>5.1200000000000002E-2</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>20</v>
@@ -1452,31 +1473,31 @@
         <v>23</v>
       </c>
       <c r="F12" s="6">
-        <v>0.0048</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="G12" s="13">
-        <v>0.0049</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="H12" s="7">
-        <v>0.0055</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="I12" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="5">
-        <v>0.0032</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="K12" s="8">
-        <v>2.0E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="L12" s="8">
-        <v>6845587.57</v>
+        <v>6845587.5700000003</v>
       </c>
       <c r="M12" s="8">
-        <v>6997574.76</v>
+        <v>6997574.7599999998</v>
       </c>
       <c r="N12" s="7">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>36</v>
@@ -1488,18 +1509,18 @@
         <v>0.125</v>
       </c>
       <c r="R12" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="7">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>20</v>
@@ -1514,22 +1535,22 @@
         <v>23</v>
       </c>
       <c r="F13" s="6">
-        <v>0.0075</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="G13" s="13">
-        <v>0.0077</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H13" s="7">
-        <v>0.0245</v>
+        <v>2.4500000000000001E-2</v>
       </c>
       <c r="I13" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="5">
-        <v>0.0205</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="K13" s="8">
-        <v>0.0175</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="L13" s="8">
         <v>2779451.17</v>
@@ -1538,7 +1559,7 @@
         <v>3754515.06</v>
       </c>
       <c r="N13" s="7">
-        <v>0.0125</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>24</v>
@@ -1547,21 +1568,21 @@
         <v>975063.89</v>
       </c>
       <c r="Q13" s="7">
-        <v>0.0302</v>
+        <v>3.0200000000000001E-2</v>
       </c>
       <c r="R13" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="7">
-        <v>0.0512</v>
+        <v>5.1200000000000002E-2</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>20</v>
@@ -1576,28 +1597,28 @@
         <v>23</v>
       </c>
       <c r="F14" s="6">
-        <v>0.0088</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="G14" s="13">
-        <v>0.1282</v>
+        <v>0.12820000000000001</v>
       </c>
       <c r="H14" s="7">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="I14" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="5">
-        <v>0.0415</v>
+        <v>4.1500000000000002E-2</v>
       </c>
       <c r="K14" s="8">
-        <v>0.0385</v>
+        <v>3.85E-2</v>
       </c>
       <c r="L14" s="8">
-        <v>4.5429333867E8</v>
+        <v>454293338.67000002</v>
       </c>
       <c r="M14" s="8">
-        <v>4.4659821084E8</v>
+        <v>446598210.83999997</v>
       </c>
       <c r="N14" s="7">
         <v>0.02</v>
@@ -1606,24 +1627,24 @@
         <v>24</v>
       </c>
       <c r="P14" s="5">
-        <v>-7695127.83</v>
+        <v>-7695127.8300000001</v>
       </c>
       <c r="Q14" s="7">
-        <v>0.0025</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="R14" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="7">
-        <v>0.0466</v>
+        <v>4.6600000000000003E-2</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>20</v>
@@ -1638,28 +1659,28 @@
         <v>23</v>
       </c>
       <c r="F15" s="6">
-        <v>0.0032</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G15" s="13">
-        <v>0.1282</v>
+        <v>0.12820000000000001</v>
       </c>
       <c r="H15" s="7">
-        <v>0.0105</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="I15" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="5">
-        <v>0.0089</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="K15" s="8">
-        <v>0.0059</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="L15" s="8">
-        <v>1.4334282507E8</v>
+        <v>143342825.06999999</v>
       </c>
       <c r="M15" s="8">
-        <v>1.442145277E8</v>
+        <v>144214527.69999999</v>
       </c>
       <c r="N15" s="7">
         <v>0.01</v>
@@ -1674,18 +1695,18 @@
         <v>0.158</v>
       </c>
       <c r="R15" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="7">
-        <v>0.0406</v>
+        <v>4.0599999999999997E-2</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>60</v>
@@ -1700,28 +1721,28 @@
         <v>23</v>
       </c>
       <c r="F16" s="6">
-        <v>0.0099</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="G16" s="6">
-        <v>0.0428</v>
+        <v>4.2799999999999998E-2</v>
       </c>
       <c r="H16" s="7">
-        <v>0.0024</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="I16" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="5">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="K16" s="8">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="L16" s="8">
-        <v>4.87862180836E9</v>
+        <v>4878621808.3599997</v>
       </c>
       <c r="M16" s="8">
-        <v>4.91213202727E9</v>
+        <v>4912132027.2700005</v>
       </c>
       <c r="N16" s="7">
         <v>0.02</v>
@@ -1730,24 +1751,24 @@
         <v>24</v>
       </c>
       <c r="P16" s="5">
-        <v>3.351021891E7</v>
+        <v>33510218.91</v>
       </c>
       <c r="Q16" s="7">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="R16" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="7">
-        <v>0.0588</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>20</v>
@@ -1762,28 +1783,28 @@
         <v>23</v>
       </c>
       <c r="F17" s="15">
-        <v>0.0168</v>
+        <v>1.6799999999999999E-2</v>
       </c>
       <c r="G17" s="15">
-        <v>0.0027</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="H17" s="16">
-        <v>-0.0086</v>
+        <v>-8.6E-3</v>
       </c>
       <c r="I17" s="17">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="5">
-        <v>-0.0073</v>
+        <v>-7.3000000000000001E-3</v>
       </c>
       <c r="K17" s="10">
-        <v>-0.0103</v>
+        <v>-1.03E-2</v>
       </c>
       <c r="L17" s="10">
-        <v>4.35847070189E9</v>
+        <v>4358470701.8900003</v>
       </c>
       <c r="M17" s="8">
-        <v>5.066872267E9</v>
+        <v>5066872267</v>
       </c>
       <c r="N17" s="7">
         <v>0.02</v>
@@ -1792,24 +1813,24 @@
         <v>24</v>
       </c>
       <c r="P17" s="5">
-        <v>7.084015651E8</v>
+        <v>708401565.10000002</v>
       </c>
       <c r="Q17" s="7">
-        <v>0.1425</v>
+        <v>0.14249999999999999</v>
       </c>
       <c r="R17" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="7">
-        <v>0.0424</v>
+        <v>4.24E-2</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
+    <row r="18" spans="1:20" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>65</v>
@@ -1826,17 +1847,17 @@
       <c r="F18" s="6"/>
       <c r="G18" s="20"/>
       <c r="H18" s="21">
-        <v>0.0485</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="I18" s="19">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="19">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="K18" s="22"/>
       <c r="L18" s="22">
-        <v>7.07786277027E9</v>
+        <v>7077862770.2700005</v>
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="19"/>
@@ -1844,29 +1865,29 @@
         <v>24</v>
       </c>
       <c r="P18" s="19">
-        <v>-7.07786277E9</v>
+        <v>-7077862770</v>
       </c>
       <c r="Q18" s="21">
-        <v>0.0815</v>
+        <v>8.1500000000000003E-2</v>
       </c>
       <c r="R18" s="19">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="21">
-        <v>0.0405</v>
+        <v>4.0500000000000001E-2</v>
       </c>
       <c r="T18" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="30" t="s">
         <v>68</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -1876,56 +1897,58 @@
         <v>23</v>
       </c>
       <c r="F19" s="6">
-        <v>0.0051</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="G19" s="6">
-        <v>0.0454</v>
+        <v>4.5400000000000003E-2</v>
       </c>
       <c r="H19" s="7">
-        <v>0.031</v>
+        <v>3.1E-2</v>
       </c>
       <c r="I19" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="5">
-        <v>0.0344</v>
+        <v>3.44E-2</v>
       </c>
       <c r="K19" s="24">
-        <v>0.0324</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M19" s="10">
-        <v>6.928555997E7</v>
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="L19" s="28">
+        <v>69079820.689999998</v>
+      </c>
+      <c r="M19" s="28">
+        <v>69285559.969999999</v>
       </c>
       <c r="N19" s="7">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="5"/>
+      <c r="P19" s="5">
+        <v>205739.28</v>
+      </c>
       <c r="Q19" s="7">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="R19" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="25"/>
       <c r="T19" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>22</v>
@@ -1934,31 +1957,31 @@
         <v>23</v>
       </c>
       <c r="F20" s="15">
-        <v>0.0129</v>
+        <v>1.29E-2</v>
       </c>
       <c r="G20" s="15">
-        <v>0.0061</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0425</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="I20" s="17">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="5">
-        <v>0.0476</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="K20" s="10">
-        <v>0.0456</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="L20" s="10">
-        <v>5.157468586E7</v>
+        <v>51574685.859999999</v>
       </c>
       <c r="M20" s="10">
-        <v>5.290540091E7</v>
+        <v>52905400.909999996</v>
       </c>
       <c r="N20" s="16">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>24</v>
@@ -1970,24 +1993,24 @@
         <v>0.1045</v>
       </c>
       <c r="R20" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="7">
-        <v>0.0622</v>
+        <v>6.2199999999999998E-2</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>22</v>
@@ -1996,31 +2019,31 @@
         <v>23</v>
       </c>
       <c r="F21" s="15">
-        <v>0.0139</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="G21" s="15">
-        <v>0.0057</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0442</v>
+        <v>4.4200000000000003E-2</v>
       </c>
       <c r="I21" s="17">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="5">
-        <v>0.0414</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="K21" s="10">
-        <v>0.0394</v>
+        <v>3.9399999999999998E-2</v>
       </c>
       <c r="L21" s="10">
-        <v>4.687558367E7</v>
+        <v>46875583.670000002</v>
       </c>
       <c r="M21" s="10">
-        <v>4.886019444E7</v>
+        <v>48860194.439999998</v>
       </c>
       <c r="N21" s="16">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>24</v>
@@ -2029,27 +2052,27 @@
         <v>1984610.77</v>
       </c>
       <c r="Q21" s="7">
-        <v>0.139</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="R21" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="7">
-        <v>0.0773</v>
+        <v>7.7299999999999994E-2</v>
       </c>
       <c r="T21" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>22</v>
@@ -2058,31 +2081,31 @@
         <v>23</v>
       </c>
       <c r="F22" s="6">
-        <v>0.0098</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="G22" s="6">
-        <v>0.2458</v>
+        <v>0.24579999999999999</v>
       </c>
       <c r="H22" s="7">
-        <v>0.0544</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="I22" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="5">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="K22" s="8">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="L22" s="8">
-        <v>3.045411588E7</v>
+        <v>30454115.879999999</v>
       </c>
       <c r="M22" s="8">
-        <v>3.116435704E7</v>
+        <v>31164357.039999999</v>
       </c>
       <c r="N22" s="7">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>24</v>
@@ -2091,10 +2114,10 @@
         <v>710241.16</v>
       </c>
       <c r="Q22" s="7">
-        <v>0.0955</v>
+        <v>9.5500000000000002E-2</v>
       </c>
       <c r="R22" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="7">
         <v>0.1145</v>
@@ -2103,15 +2126,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
+    <row r="23" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>22</v>
@@ -2120,31 +2143,31 @@
         <v>23</v>
       </c>
       <c r="F23" s="6">
-        <v>0.0014</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G23" s="6">
-        <v>0.0024</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="H23" s="7">
-        <v>0.0395</v>
+        <v>3.95E-2</v>
       </c>
       <c r="I23" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="5">
-        <v>0.0385</v>
+        <v>3.85E-2</v>
       </c>
       <c r="K23" s="8">
-        <v>0.0375</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="L23" s="8">
-        <v>2.398363698E7</v>
+        <v>23983636.98</v>
       </c>
       <c r="M23" s="8">
-        <v>2.156797879E7</v>
+        <v>21567978.789999999</v>
       </c>
       <c r="N23" s="7">
-        <v>0.0025</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>24</v>
@@ -2153,27 +2176,27 @@
         <v>-2415658.19</v>
       </c>
       <c r="Q23" s="7">
-        <v>0.0018</v>
+        <v>1.8E-3</v>
       </c>
       <c r="R23" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="7">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
+    <row r="24" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>22</v>
@@ -2182,43 +2205,43 @@
         <v>23</v>
       </c>
       <c r="F24" s="6">
-        <v>0.0023</v>
+        <v>2.3E-3</v>
       </c>
       <c r="G24" s="6">
-        <v>0.0033</v>
+        <v>3.3E-3</v>
       </c>
       <c r="H24" s="7">
-        <v>0.0418</v>
+        <v>4.1799999999999997E-2</v>
       </c>
       <c r="I24" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="5">
-        <v>0.0405</v>
+        <v>4.0500000000000001E-2</v>
       </c>
       <c r="K24" s="8">
-        <v>0.0395</v>
+        <v>3.95E-2</v>
       </c>
       <c r="L24" s="8">
-        <v>1.2002E10</v>
+        <v>12002000000</v>
       </c>
       <c r="M24" s="8">
-        <v>1.012591384344E10</v>
+        <v>10125913843.440001</v>
       </c>
       <c r="N24" s="7">
-        <v>0.0025</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="P24" s="5">
-        <v>-1.876086157E9</v>
+        <v>-1876086157</v>
       </c>
       <c r="Q24" s="7">
-        <v>0.0022</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="R24" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S24" s="26">
         <v>0.04</v>
@@ -2227,15 +2250,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
+    <row r="25" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>76</v>
+      <c r="C25" s="30" t="s">
+        <v>75</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>22</v>
@@ -2244,58 +2267,60 @@
         <v>23</v>
       </c>
       <c r="F25" s="6">
-        <v>0.0112</v>
+        <v>1.12E-2</v>
       </c>
       <c r="G25" s="6">
-        <v>0.0145</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="H25" s="7">
         <v>0.1512</v>
       </c>
       <c r="I25" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="5">
-        <v>0.1412</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="K25" s="8">
-        <v>0.1382</v>
-      </c>
-      <c r="L25" s="27">
-        <v>3.740140136E7</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>77</v>
+        <v>0.13819999999999999</v>
+      </c>
+      <c r="L25" s="29">
+        <v>37401401.359999999</v>
+      </c>
+      <c r="M25" s="31">
+        <v>85094442.209999993</v>
       </c>
       <c r="N25" s="7">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="P25" s="5"/>
+      <c r="P25" s="5">
+        <v>47693040.850000001</v>
+      </c>
       <c r="Q25" s="7">
         <v>0.108</v>
       </c>
       <c r="R25" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="7">
         <v>0.121</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>22</v>
@@ -2304,16 +2329,16 @@
         <v>23</v>
       </c>
       <c r="F26" s="15">
-        <v>0.0067</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="G26" s="15">
-        <v>0.2388</v>
+        <v>0.23880000000000001</v>
       </c>
       <c r="H26" s="16">
-        <v>0.1582</v>
+        <v>0.15820000000000001</v>
       </c>
       <c r="I26" s="17">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="5">
         <v>0.153</v>
@@ -2322,10 +2347,10 @@
         <v>0.15</v>
       </c>
       <c r="L26" s="10">
-        <v>6.67716567731E9</v>
+        <v>6677165677.3100004</v>
       </c>
       <c r="M26" s="10">
-        <v>7.57833196102E9</v>
+        <v>7578331961.0200005</v>
       </c>
       <c r="N26" s="16">
         <v>0.02</v>
@@ -2334,30 +2359,30 @@
         <v>24</v>
       </c>
       <c r="P26" s="17">
-        <v>9.011662837E8</v>
+        <v>901166283.70000005</v>
       </c>
       <c r="Q26" s="7">
-        <v>0.1465</v>
+        <v>0.14649999999999999</v>
       </c>
       <c r="R26" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="7">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="28">
-        <v>30.0</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <v>30</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>22</v>
@@ -2366,28 +2391,28 @@
         <v>23</v>
       </c>
       <c r="F27" s="15">
-        <v>0.0012</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G27" s="15">
-        <v>0.0034</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I27" s="17">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="5">
-        <v>0.058</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="K27" s="10">
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="L27" s="10">
-        <v>3.66158300005E9</v>
+        <v>3661583000.0500002</v>
       </c>
       <c r="M27" s="10">
-        <v>3.76087587965E9</v>
+        <v>3760875879.6500001</v>
       </c>
       <c r="N27" s="16">
         <v>0.01</v>
@@ -2396,25 +2421,26 @@
         <v>24</v>
       </c>
       <c r="P27" s="17">
-        <v>9.92928796E7</v>
+        <v>99292879.599999994</v>
       </c>
       <c r="Q27" s="7">
-        <v>0.0695</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="R27" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="7">
-        <v>0.0346</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="T27" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>